--- a/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
@@ -725,17 +725,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -768,16 +760,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260130</t>

--- a/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
@@ -725,11 +725,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260130</t>
@@ -760,8 +780,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1833025</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>183325</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>20260130</t>

--- a/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>183325</t>
+          <t>1833025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -834,6 +834,116 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1833026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1833026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1833026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1833026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>S00028</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:F3"/>

--- a/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00028_1833_Wealth직장인연금보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -760,11 +760,7 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n">
         <v>1</v>
       </c>
@@ -782,22 +778,22 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -815,13 +811,8 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -829,116 +820,6 @@
         </is>
       </c>
       <c r="L8" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1833026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>S00028</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
